--- a/Valeri_Pmax_Eight_Summer_Sales_2026.xlsx
+++ b/Valeri_Pmax_Eight_Summer_Sales_2026.xlsx
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="DO94" s="1" t="n">
-        <v>46219</v>
+        <v>46204</v>
       </c>
       <c r="DP94" s="1" t="n">
         <v>46265</v>
@@ -5452,7 +5452,7 @@
         </is>
       </c>
       <c r="DO95" s="1" t="n">
-        <v>46219</v>
+        <v>46204</v>
       </c>
       <c r="DP95" s="1" t="n">
         <v>46265</v>
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="DO96" s="1" t="n">
-        <v>46219</v>
+        <v>46204</v>
       </c>
       <c r="DP96" s="1" t="n">
         <v>46265</v>
@@ -5618,7 +5618,7 @@
         </is>
       </c>
       <c r="DO97" s="1" t="n">
-        <v>46219</v>
+        <v>46204</v>
       </c>
       <c r="DP97" s="1" t="n">
         <v>46265</v>
@@ -5701,7 +5701,7 @@
         </is>
       </c>
       <c r="DO98" s="1" t="n">
-        <v>46219</v>
+        <v>46204</v>
       </c>
       <c r="DP98" s="1" t="n">
         <v>46265</v>

--- a/Valeri_Pmax_Eight_Summer_Sales_2026.xlsx
+++ b/Valeri_Pmax_Eight_Summer_Sales_2026.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EM112"/>
+  <dimension ref="A1:EM148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1327,127 +1327,127 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>ARPYES Summer Sale</t>
+          <t>ARPYES έως -30%</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>ARPYES up to -30%</t>
+          <t>Boho Chic ARPYES</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>ARPYES έως -30%</t>
+          <t>Καλοκαιρινές Εκπτώσεις</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
+          <t>Premium Boho Στυλ</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>Έκπτωση έως -30%</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Δωρεάν Επιστροφές Πάντα</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>Boho Κομμάτια ARPYES</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>Αγόρασε στο Valeri.gr</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>ARPYES up to -30% Off</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Premium Boho Chic</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Summer Sale Is Here</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
           <t>Shop ARPYES Now</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>ARPYES σε Έκπτωση</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>ARPYES | Valeri.gr</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>ARPYES Καλοκαιρινή Μόδα</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>Έκπτωση έως -30% ARPYES</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>Καλοκαιρινές Εκπτώσεις</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Δωρεάν Επιστροφές Πάντα</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Παράδοση σε 2-3 Μέρες</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Αγόρασε στο Valeri.gr</t>
-        </is>
-      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>Γυναικεία Μόδα Ελλάδα</t>
+          <t>Boho Chic, Elevated</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Shop the Designer Sale</t>
+          <t>Effortless Summer Style</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>Your Summer Upgrade</t>
+          <t>Free Returns Always</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>ARPYES Summer Sale στο Valeri.gr – Εκπτώσεις έως -30% &amp; Δωρεάν Επιστροφές</t>
+          <t>ARPYES Summer Sales – Premium Boho Chic κομμάτια έως -30% στο Valeri.gr</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>Shop the Designer Sale at Valeri.gr – ARPYES up to -30% Off</t>
+          <t>Shop the ARPYES Summer Sale at Valeri.gr – Premium Boho Chic, up to -30% Off</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>Your summer wardrobe just got an upgrade – ARPYES έως -30% στο Valeri.gr</t>
+          <t>Ανακάλυψε το Boho Chic στυλ της ARPYES με έκπτωση έως -30% | Valeri.gr</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>Γυναικεία Μόδα ARPYES σε Έκπτωση | Παράδοση 2-3 Μέρες σε όλη την Ελλάδα</t>
+          <t>Elevate Your Summer Wardrobe – ARPYES Premium Boho Chic up to -30% Off</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Ανακάλυψε τη Συλλογή ARPYES με έκπτωση έως -30% μόνο στο Valeri.gr</t>
+          <t>Καλοκαιρινές Εκπτώσεις ARPYES έως -30% | Δωρεάν Επιστροφές &amp; Παράδοση 2-3 Μέρες</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>Ανακάλυψε τη συλλογή ARPYES με έκπτωση έως -30%. Αγόρασε online στο Valeri.gr.</t>
+          <t>Ανακάλυψε τη συλλογή ARPYES με premium boho chic στυλ και έκπτωση έως -30%.</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>Shop the Designer Sale at Valeri.gr. ARPYES up to -30% off. Free returns always.</t>
+          <t>Shop the ARPYES Summer Sale at Valeri.gr. Premium boho chic, up to -30% off.</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>Γυναικεία μόδα ARPYES σε έκπτωση. Δωρεάν επιστροφές &amp; παράδοση 2-3 μέρες.</t>
+          <t>Καλοκαιρινές εκπτώσεις έως -30% σε boho chic κομμάτια. Δωρεάν επιστροφές.</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>Το καλοκαιρινό σου wardrobe αναβαθμίζεται. ARPYES έως -30% μόνο στο Valeri.gr.</t>
+          <t>Premium boho chic από την ARPYES. Παράδοση 2-3 μέρες σε όλη την Ελλάδα.</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>Στυλάτα κομμάτια ARPYES με έκπτωση. Παράδοση 2-3 μέρες σε όλη την Ελλάδα.</t>
+          <t>Elevate your summer wardrobe with ARPYES boho chic. Up to -30% off online.</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="DY9" t="inlineStr">
         <is>
-          <t>arpyes καλοκαιρινή συλλογή</t>
+          <t>arpyes καλοκαιρινές εκπτώσεις</t>
         </is>
       </c>
       <c r="EG9" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="DY10" t="inlineStr">
         <is>
-          <t>arpyes φόρεμα</t>
+          <t>arpyes καλοκαιρινή συλλογή</t>
         </is>
       </c>
       <c r="EG10" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="DY11" t="inlineStr">
         <is>
-          <t>arpyes online</t>
+          <t>arpyes boho</t>
         </is>
       </c>
       <c r="EG11" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="DY12" t="inlineStr">
         <is>
-          <t>αγορά arpyes ρούχα</t>
+          <t>arpyes boho chic</t>
         </is>
       </c>
       <c r="EG12" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="DY13" t="inlineStr">
         <is>
-          <t>arpyes valeri</t>
+          <t>arpyes φόρεμα</t>
         </is>
       </c>
       <c r="EG13" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="DY14" t="inlineStr">
         <is>
-          <t>arpyes προσφορές</t>
+          <t>arpyes φορέματα</t>
         </is>
       </c>
       <c r="EG14" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="DY15" t="inlineStr">
         <is>
-          <t>arpyes clothing sale</t>
+          <t>arpyes online</t>
         </is>
       </c>
       <c r="EG15" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="DY16" t="inlineStr">
         <is>
-          <t>arpyes summer sale</t>
+          <t>arpyes valeri</t>
         </is>
       </c>
       <c r="EG16" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="DY17" t="inlineStr">
         <is>
-          <t>buy arpyes online</t>
+          <t>arpyes προσφορές</t>
         </is>
       </c>
       <c r="EG17" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="DY18" t="inlineStr">
         <is>
-          <t>arpyes dresses</t>
+          <t>arpyes ρούχα έκπτωση</t>
         </is>
       </c>
       <c r="EG18" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="DY19" t="inlineStr">
         <is>
-          <t>designer sale γυναικεία ρούχα</t>
+          <t>arpyes boho φόρεμα</t>
         </is>
       </c>
       <c r="EG19" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="DY20" t="inlineStr">
         <is>
-          <t>επώνυμα ρούχα εκπτώσεις</t>
+          <t>arpyes premium ρούχα</t>
         </is>
       </c>
       <c r="EG20" t="inlineStr">
@@ -2118,142 +2118,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>CKONTOVA | Summer Sales | BOFU</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>CKONTOVA Summer Sale</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>CKONTOVA -20%</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>Shop CKONTOVA Now</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>CKONTOVA σε Έκπτωση</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>CKONTOVA | Valeri.gr</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>CKONTOVA Καλοκαιρινή Μόδα</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>Έκπτωση -20% CKONTOVA</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>Καλοκαιρινές Εκπτώσεις</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>Δωρεάν Επιστροφές Πάντα</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Παράδοση σε 2-3 Μέρες</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Αγόρασε στο Valeri.gr</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Γυναικεία Μόδα Ελλάδα</t>
-        </is>
-      </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>Shop the Designer Sale</t>
-        </is>
-      </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>Your Summer Upgrade</t>
-        </is>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>Summer Sale Is Here</t>
-        </is>
-      </c>
-      <c r="BC21" t="inlineStr">
-        <is>
-          <t>CKONTOVA Summer Sale στο Valeri.gr – Εκπτώσεις -20% &amp; Δωρεάν Επιστροφές</t>
-        </is>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>Shop the Designer Sale at Valeri.gr – CKONTOVA -20% Off</t>
-        </is>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>Your summer wardrobe just got an upgrade – CKONTOVA -20% στο Valeri.gr</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>Γυναικεία Μόδα CKONTOVA σε Έκπτωση | Παράδοση 2-3 Μέρες σε όλη την Ελλάδα</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>Ανακάλυψε τη Συλλογή CKONTOVA με έκπτωση -20% μόνο στο Valeri.gr</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>Ανακάλυψε τη συλλογή CKONTOVA με έκπτωση -20%. Αγόρασε online στο Valeri.gr.</t>
-        </is>
-      </c>
-      <c r="BI21" t="inlineStr">
-        <is>
-          <t>Shop the Designer Sale at Valeri.gr. CKONTOVA -20% off. Free returns always.</t>
-        </is>
-      </c>
-      <c r="BJ21" t="inlineStr">
-        <is>
-          <t>Γυναικεία μόδα CKONTOVA σε έκπτωση. Δωρεάν επιστροφές &amp; παράδοση 2-3 μέρες.</t>
-        </is>
-      </c>
-      <c r="BK21" t="inlineStr">
-        <is>
-          <t>Το καλοκαιρινό σου wardrobe αναβαθμίζεται. CKONTOVA -20% μόνο στο Valeri.gr.</t>
-        </is>
-      </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>Στυλάτα κομμάτια CKONTOVA με έκπτωση. Παράδοση 2-3 μέρες σε όλη την Ελλάδα.</t>
-        </is>
-      </c>
-      <c r="CF21" t="inlineStr">
-        <is>
-          <t>https://valeri.gr/ckontova-el</t>
-        </is>
-      </c>
-      <c r="CH21" t="inlineStr">
-        <is>
-          <t>CKONTOVA Buyers &amp; Greek Fashion Enthusiasts</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY21" t="inlineStr">
+        <is>
+          <t>αγορά arpyes ρούχα</t>
         </is>
       </c>
       <c r="EG21" t="inlineStr">
@@ -2266,14 +2136,14 @@
           <t>Enabled</t>
         </is>
       </c>
+      <c r="EJ21" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
       <c r="EK21" t="inlineStr">
         <is>
           <t>Approved</t>
-        </is>
-      </c>
-      <c r="EL21" t="inlineStr">
-        <is>
-          <t>Average</t>
         </is>
       </c>
     </row>
@@ -2285,17 +2155,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>CKONTOVA | Summer Sales | BOFU</t>
-        </is>
-      </c>
-      <c r="DV22" t="inlineStr">
-        <is>
-          <t>* /</t>
-        </is>
-      </c>
-      <c r="DX22" t="inlineStr">
-        <is>
-          <t>Subdivision</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY22" t="inlineStr">
+        <is>
+          <t>arpyes τοπ</t>
         </is>
       </c>
       <c r="EG22" t="inlineStr">
@@ -2311,6 +2176,11 @@
       <c r="EJ22" t="inlineStr">
         <is>
           <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK22" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -2322,17 +2192,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>CKONTOVA | Summer Sales | BOFU</t>
-        </is>
-      </c>
-      <c r="DV23" t="inlineStr">
-        <is>
-          <t>* / Brand=*</t>
-        </is>
-      </c>
-      <c r="DX23" t="inlineStr">
-        <is>
-          <t>Excluded</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY23" t="inlineStr">
+        <is>
+          <t>arpyes μπλούζες</t>
         </is>
       </c>
       <c r="EG23" t="inlineStr">
@@ -2348,6 +2213,11 @@
       <c r="EJ23" t="inlineStr">
         <is>
           <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK23" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -2359,17 +2229,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>CKONTOVA | Summer Sales | BOFU</t>
-        </is>
-      </c>
-      <c r="DV24" t="inlineStr">
-        <is>
-          <t>* / Brand='ckontova'</t>
-        </is>
-      </c>
-      <c r="DX24" t="inlineStr">
-        <is>
-          <t>Biddable</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY24" t="inlineStr">
+        <is>
+          <t>arpyes παντελόνια</t>
         </is>
       </c>
       <c r="EG24" t="inlineStr">
@@ -2385,6 +2250,11 @@
       <c r="EJ24" t="inlineStr">
         <is>
           <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK24" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -2396,12 +2266,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>CKONTOVA | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY25" t="inlineStr">
         <is>
-          <t>ckontova γυναικεία ρούχα</t>
+          <t>arpyes φούστες</t>
         </is>
       </c>
       <c r="EG25" t="inlineStr">
@@ -2433,12 +2303,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>CKONTOVA | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY26" t="inlineStr">
         <is>
-          <t>ckontova εκπτώσεις</t>
+          <t>arpyes σετ</t>
         </is>
       </c>
       <c r="EG26" t="inlineStr">
@@ -2470,12 +2340,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>CKONTOVA | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY27" t="inlineStr">
         <is>
-          <t>ckontova καλοκαιρινή συλλογή</t>
+          <t>boho chic γυναικεία ρούχα</t>
         </is>
       </c>
       <c r="EG27" t="inlineStr">
@@ -2507,12 +2377,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>CKONTOVA | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY28" t="inlineStr">
         <is>
-          <t>ckontova φόρεμα</t>
+          <t>boho chic φορέματα</t>
         </is>
       </c>
       <c r="EG28" t="inlineStr">
@@ -2544,12 +2414,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>CKONTOVA | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY29" t="inlineStr">
         <is>
-          <t>ckontova online</t>
+          <t>boho φορέματα έκπτωση</t>
         </is>
       </c>
       <c r="EG29" t="inlineStr">
@@ -2581,12 +2451,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>CKONTOVA | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY30" t="inlineStr">
         <is>
-          <t>αγορά ckontova ρούχα</t>
+          <t>boho ρούχα ελλάδα</t>
         </is>
       </c>
       <c r="EG30" t="inlineStr">
@@ -2618,12 +2488,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>CKONTOVA | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY31" t="inlineStr">
         <is>
-          <t>ckontova valeri</t>
+          <t>boho chic μόδα</t>
         </is>
       </c>
       <c r="EG31" t="inlineStr">
@@ -2655,12 +2525,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>CKONTOVA | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY32" t="inlineStr">
         <is>
-          <t>ckontova προσφορές</t>
+          <t>καλοκαιρινά φορέματα έκπτωση</t>
         </is>
       </c>
       <c r="EG32" t="inlineStr">
@@ -2692,12 +2562,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>CKONTOVA | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY33" t="inlineStr">
         <is>
-          <t>ckontova clothing sale</t>
+          <t>γυναικεία ρούχα έκπτωση</t>
         </is>
       </c>
       <c r="EG33" t="inlineStr">
@@ -2729,12 +2599,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>CKONTOVA | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY34" t="inlineStr">
         <is>
-          <t>ckontova summer sale</t>
+          <t>επώνυμα γυναικεία ρούχα εκπτώσεις</t>
         </is>
       </c>
       <c r="EG34" t="inlineStr">
@@ -2766,12 +2636,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>CKONTOVA | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY35" t="inlineStr">
         <is>
-          <t>buy ckontova online</t>
+          <t>designer boho ρούχα</t>
         </is>
       </c>
       <c r="EG35" t="inlineStr">
@@ -2803,12 +2673,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>CKONTOVA | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY36" t="inlineStr">
         <is>
-          <t>ckontova dresses</t>
+          <t>premium boho ρούχα ελλάδα</t>
         </is>
       </c>
       <c r="EG36" t="inlineStr">
@@ -2840,12 +2710,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>CKONTOVA | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY37" t="inlineStr">
         <is>
-          <t>designer sale γυναικεία ρούχα</t>
+          <t>arpyes clothing</t>
         </is>
       </c>
       <c r="EG37" t="inlineStr">
@@ -2877,12 +2747,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>CKONTOVA | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY38" t="inlineStr">
         <is>
-          <t>επώνυμα ρούχα εκπτώσεις</t>
+          <t>arpyes clothing sale</t>
         </is>
       </c>
       <c r="EG38" t="inlineStr">
@@ -2914,142 +2784,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>LA CHAINE | Summer Sales | BOFU</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>LA CHAINE Summer Sale</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>LA CHAINE -20%</t>
-        </is>
-      </c>
-      <c r="AP39" t="inlineStr">
-        <is>
-          <t>Shop LA CHAINE Now</t>
-        </is>
-      </c>
-      <c r="AQ39" t="inlineStr">
-        <is>
-          <t>LA CHAINE σε Έκπτωση</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>LA CHAINE | Valeri.gr</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr">
-        <is>
-          <t>LA CHAINE Καλοκαιρινή Μόδα</t>
-        </is>
-      </c>
-      <c r="AT39" t="inlineStr">
-        <is>
-          <t>Έκπτωση -20% LA CHAINE</t>
-        </is>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>Καλοκαιρινές Εκπτώσεις</t>
-        </is>
-      </c>
-      <c r="AV39" t="inlineStr">
-        <is>
-          <t>Δωρεάν Επιστροφές Πάντα</t>
-        </is>
-      </c>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Παράδοση σε 2-3 Μέρες</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Αγόρασε στο Valeri.gr</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Γυναικεία Μόδα Ελλάδα</t>
-        </is>
-      </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>Shop the Designer Sale</t>
-        </is>
-      </c>
-      <c r="BA39" t="inlineStr">
-        <is>
-          <t>Your Summer Upgrade</t>
-        </is>
-      </c>
-      <c r="BB39" t="inlineStr">
-        <is>
-          <t>Summer Sale Is Here</t>
-        </is>
-      </c>
-      <c r="BC39" t="inlineStr">
-        <is>
-          <t>LA CHAINE Summer Sale στο Valeri.gr – Εκπτώσεις -20% &amp; Δωρεάν Επιστροφές</t>
-        </is>
-      </c>
-      <c r="BD39" t="inlineStr">
-        <is>
-          <t>Shop the Designer Sale at Valeri.gr – LA CHAINE -20% Off</t>
-        </is>
-      </c>
-      <c r="BE39" t="inlineStr">
-        <is>
-          <t>Your summer wardrobe just got an upgrade – LA CHAINE -20% στο Valeri.gr</t>
-        </is>
-      </c>
-      <c r="BF39" t="inlineStr">
-        <is>
-          <t>Γυναικεία Μόδα LA CHAINE σε Έκπτωση | Παράδοση 2-3 Μέρες σε όλη την Ελλάδα</t>
-        </is>
-      </c>
-      <c r="BG39" t="inlineStr">
-        <is>
-          <t>Ανακάλυψε τη Συλλογή LA CHAINE με έκπτωση -20% μόνο στο Valeri.gr</t>
-        </is>
-      </c>
-      <c r="BH39" t="inlineStr">
-        <is>
-          <t>Ανακάλυψε τη συλλογή LA CHAINE με έκπτωση -20%. Αγόρασε online στο Valeri.gr.</t>
-        </is>
-      </c>
-      <c r="BI39" t="inlineStr">
-        <is>
-          <t>Shop the Designer Sale at Valeri.gr. LA CHAINE -20% off. Free returns always.</t>
-        </is>
-      </c>
-      <c r="BJ39" t="inlineStr">
-        <is>
-          <t>Γυναικεία μόδα LA CHAINE σε έκπτωση. Δωρεάν επιστροφές &amp; παράδοση 2-3 μέρες.</t>
-        </is>
-      </c>
-      <c r="BK39" t="inlineStr">
-        <is>
-          <t>Το καλοκαιρινό σου wardrobe αναβαθμίζεται. LA CHAINE -20% μόνο στο Valeri.gr.</t>
-        </is>
-      </c>
-      <c r="BL39" t="inlineStr">
-        <is>
-          <t>Στυλάτα κομμάτια LA CHAINE με έκπτωση. Παράδοση 2-3 μέρες σε όλη την Ελλάδα.</t>
-        </is>
-      </c>
-      <c r="CF39" t="inlineStr">
-        <is>
-          <t>https://valeri.gr/la-chaine-el</t>
-        </is>
-      </c>
-      <c r="CH39" t="inlineStr">
-        <is>
-          <t>LA CHAINE Buyers &amp; Greek Fashion Enthusiasts</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY39" t="inlineStr">
+        <is>
+          <t>arpyes summer sale</t>
         </is>
       </c>
       <c r="EG39" t="inlineStr">
@@ -3062,14 +2802,14 @@
           <t>Enabled</t>
         </is>
       </c>
+      <c r="EJ39" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
       <c r="EK39" t="inlineStr">
         <is>
           <t>Approved</t>
-        </is>
-      </c>
-      <c r="EL39" t="inlineStr">
-        <is>
-          <t>Average</t>
         </is>
       </c>
     </row>
@@ -3081,17 +2821,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>LA CHAINE | Summer Sales | BOFU</t>
-        </is>
-      </c>
-      <c r="DV40" t="inlineStr">
-        <is>
-          <t>* /</t>
-        </is>
-      </c>
-      <c r="DX40" t="inlineStr">
-        <is>
-          <t>Subdivision</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY40" t="inlineStr">
+        <is>
+          <t>arpyes dresses</t>
         </is>
       </c>
       <c r="EG40" t="inlineStr">
@@ -3107,6 +2842,11 @@
       <c r="EJ40" t="inlineStr">
         <is>
           <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK40" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -3118,17 +2858,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>LA CHAINE | Summer Sales | BOFU</t>
-        </is>
-      </c>
-      <c r="DV41" t="inlineStr">
-        <is>
-          <t>* / Brand=*</t>
-        </is>
-      </c>
-      <c r="DX41" t="inlineStr">
-        <is>
-          <t>Excluded</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY41" t="inlineStr">
+        <is>
+          <t>arpyes boho dress</t>
         </is>
       </c>
       <c r="EG41" t="inlineStr">
@@ -3144,6 +2879,11 @@
       <c r="EJ41" t="inlineStr">
         <is>
           <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK41" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -3155,17 +2895,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>LA CHAINE | Summer Sales | BOFU</t>
-        </is>
-      </c>
-      <c r="DV42" t="inlineStr">
-        <is>
-          <t>* / Brand='la chaine'</t>
-        </is>
-      </c>
-      <c r="DX42" t="inlineStr">
-        <is>
-          <t>Biddable</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY42" t="inlineStr">
+        <is>
+          <t>buy arpyes online</t>
         </is>
       </c>
       <c r="EG42" t="inlineStr">
@@ -3181,6 +2916,11 @@
       <c r="EJ42" t="inlineStr">
         <is>
           <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK42" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -3192,12 +2932,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>LA CHAINE | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY43" t="inlineStr">
         <is>
-          <t>la chaine γυναικεία ρούχα</t>
+          <t>arpyes boho chic dress</t>
         </is>
       </c>
       <c r="EG43" t="inlineStr">
@@ -3229,12 +2969,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>LA CHAINE | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY44" t="inlineStr">
         <is>
-          <t>la chaine εκπτώσεις</t>
+          <t>arpyes discount</t>
         </is>
       </c>
       <c r="EG44" t="inlineStr">
@@ -3266,12 +3006,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>LA CHAINE | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY45" t="inlineStr">
         <is>
-          <t>la chaine καλοκαιρινή συλλογή</t>
+          <t>shop arpyes</t>
         </is>
       </c>
       <c r="EG45" t="inlineStr">
@@ -3303,12 +3043,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>LA CHAINE | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY46" t="inlineStr">
         <is>
-          <t>la chaine φόρεμα</t>
+          <t>arpyes premium fashion</t>
         </is>
       </c>
       <c r="EG46" t="inlineStr">
@@ -3340,12 +3080,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>LA CHAINE | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY47" t="inlineStr">
         <is>
-          <t>la chaine online</t>
+          <t>boho chic dresses</t>
         </is>
       </c>
       <c r="EG47" t="inlineStr">
@@ -3377,12 +3117,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>LA CHAINE | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY48" t="inlineStr">
         <is>
-          <t>αγορά la chaine ρούχα</t>
+          <t>boho chic clothing</t>
         </is>
       </c>
       <c r="EG48" t="inlineStr">
@@ -3414,12 +3154,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>LA CHAINE | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY49" t="inlineStr">
         <is>
-          <t>la chaine valeri</t>
+          <t>boho chic summer dress</t>
         </is>
       </c>
       <c r="EG49" t="inlineStr">
@@ -3451,12 +3191,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>LA CHAINE | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY50" t="inlineStr">
         <is>
-          <t>la chaine προσφορές</t>
+          <t>premium boho fashion</t>
         </is>
       </c>
       <c r="EG50" t="inlineStr">
@@ -3488,12 +3228,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>LA CHAINE | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY51" t="inlineStr">
         <is>
-          <t>la chaine clothing sale</t>
+          <t>boho chic sale</t>
         </is>
       </c>
       <c r="EG51" t="inlineStr">
@@ -3525,12 +3265,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>LA CHAINE | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY52" t="inlineStr">
         <is>
-          <t>la chaine summer sale</t>
+          <t>greek boho brand</t>
         </is>
       </c>
       <c r="EG52" t="inlineStr">
@@ -3562,12 +3302,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>LA CHAINE | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY53" t="inlineStr">
         <is>
-          <t>buy la chaine online</t>
+          <t>summer dresses sale</t>
         </is>
       </c>
       <c r="EG53" t="inlineStr">
@@ -3599,12 +3339,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>LA CHAINE | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY54" t="inlineStr">
         <is>
-          <t>la chaine dresses</t>
+          <t>designer boho clothing</t>
         </is>
       </c>
       <c r="EG54" t="inlineStr">
@@ -3636,12 +3376,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>LA CHAINE | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY55" t="inlineStr">
         <is>
-          <t>designer sale γυναικεία ρούχα</t>
+          <t>women boho chic outfit</t>
         </is>
       </c>
       <c r="EG55" t="inlineStr">
@@ -3673,12 +3413,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>LA CHAINE | Summer Sales | BOFU</t>
+          <t>ARPYES | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY56" t="inlineStr">
         <is>
-          <t>επώνυμα ρούχα εκπτώσεις</t>
+          <t>boho chic dress greece</t>
         </is>
       </c>
       <c r="EG56" t="inlineStr">
@@ -3710,142 +3450,142 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+          <t>CKONTOVA | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>MALLORY THE LABEL Summer Sale</t>
+          <t>CKONTOVA Summer Sale</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>MALLORY THE LABEL -20%</t>
+          <t>CKONTOVA -20%</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>Shop MALLORY THE LABEL Now</t>
+          <t>Shop CKONTOVA Now</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>MALLORY THE LABEL σε Έκπτωση</t>
+          <t>CKONTOVA σε Έκπτωση</t>
         </is>
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>MALLORY THE LABEL | Valeri.gr</t>
+          <t>CKONTOVA | Valeri.gr</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>Έκπτωση -20% MALLORY THE LABEL</t>
+          <t>CKONTOVA Καλοκαιρινή Μόδα</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>Έκπτωση -20% CKONTOVA</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>Καλοκαιρινές Εκπτώσεις</t>
         </is>
       </c>
-      <c r="AU57" t="inlineStr">
+      <c r="AV57" t="inlineStr">
         <is>
           <t>Δωρεάν Επιστροφές Πάντα</t>
         </is>
       </c>
-      <c r="AV57" t="inlineStr">
+      <c r="AW57" t="inlineStr">
         <is>
           <t>Παράδοση σε 2-3 Μέρες</t>
         </is>
       </c>
-      <c r="AW57" t="inlineStr">
+      <c r="AX57" t="inlineStr">
         <is>
           <t>Αγόρασε στο Valeri.gr</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
+      <c r="AY57" t="inlineStr">
         <is>
           <t>Γυναικεία Μόδα Ελλάδα</t>
         </is>
       </c>
-      <c r="AY57" t="inlineStr">
+      <c r="AZ57" t="inlineStr">
         <is>
           <t>Shop the Designer Sale</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
+      <c r="BA57" t="inlineStr">
         <is>
           <t>Your Summer Upgrade</t>
         </is>
       </c>
-      <c r="BA57" t="inlineStr">
+      <c r="BB57" t="inlineStr">
         <is>
           <t>Summer Sale Is Here</t>
         </is>
       </c>
-      <c r="BB57" t="inlineStr">
-        <is>
-          <t>Στυλάτα Γυναικεία Ρούχα</t>
-        </is>
-      </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>MALLORY THE LABEL Summer Sale στο Valeri.gr – Εκπτώσεις -20% &amp; Δωρεάν Επιστροφές</t>
+          <t>CKONTOVA Summer Sale στο Valeri.gr – Εκπτώσεις -20% &amp; Δωρεάν Επιστροφές</t>
         </is>
       </c>
       <c r="BD57" t="inlineStr">
         <is>
-          <t>Shop the Designer Sale at Valeri.gr – MALLORY THE LABEL -20% Off</t>
+          <t>Shop the Designer Sale at Valeri.gr – CKONTOVA -20% Off</t>
         </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
-          <t>Your summer wardrobe just got an upgrade – MALLORY THE LABEL -20% στο Valeri.gr</t>
+          <t>Your summer wardrobe just got an upgrade – CKONTOVA -20% στο Valeri.gr</t>
         </is>
       </c>
       <c r="BF57" t="inlineStr">
         <is>
-          <t>Γυναικεία Μόδα MALLORY THE LABEL σε Έκπτωση | Παράδοση 2-3 Μέρες σε όλη την Ελλάδα</t>
+          <t>Γυναικεία Μόδα CKONTOVA σε Έκπτωση | Παράδοση 2-3 Μέρες σε όλη την Ελλάδα</t>
         </is>
       </c>
       <c r="BG57" t="inlineStr">
         <is>
-          <t>Ανακάλυψε τη Συλλογή MALLORY THE LABEL με έκπτωση -20% μόνο στο Valeri.gr</t>
+          <t>Ανακάλυψε τη Συλλογή CKONTOVA με έκπτωση -20% μόνο στο Valeri.gr</t>
         </is>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>Ανακάλυψε τη συλλογή MALLORY THE LABEL με έκπτωση -20%. Αγόρασε online στο Valeri.gr.</t>
+          <t>Ανακάλυψε τη συλλογή CKONTOVA με έκπτωση -20%. Αγόρασε online στο Valeri.gr.</t>
         </is>
       </c>
       <c r="BI57" t="inlineStr">
         <is>
-          <t>Shop the Designer Sale at Valeri.gr. MALLORY THE LABEL -20% off. Free returns always.</t>
+          <t>Shop the Designer Sale at Valeri.gr. CKONTOVA -20% off. Free returns always.</t>
         </is>
       </c>
       <c r="BJ57" t="inlineStr">
         <is>
-          <t>Γυναικεία μόδα MALLORY THE LABEL σε έκπτωση. Δωρεάν επιστροφές &amp; παράδοση 2-3 μέρες.</t>
+          <t>Γυναικεία μόδα CKONTOVA σε έκπτωση. Δωρεάν επιστροφές &amp; παράδοση 2-3 μέρες.</t>
         </is>
       </c>
       <c r="BK57" t="inlineStr">
         <is>
-          <t>Το καλοκαιρινό σου wardrobe αναβαθμίζεται. MALLORY THE LABEL -20% μόνο στο Valeri.gr.</t>
+          <t>Το καλοκαιρινό σου wardrobe αναβαθμίζεται. CKONTOVA -20% μόνο στο Valeri.gr.</t>
         </is>
       </c>
       <c r="BL57" t="inlineStr">
         <is>
-          <t>Στυλάτα κομμάτια MALLORY THE LABEL με έκπτωση. Παράδοση 2-3 μέρες σε όλη την Ελλάδα.</t>
+          <t>Στυλάτα κομμάτια CKONTOVA με έκπτωση. Παράδοση 2-3 μέρες σε όλη την Ελλάδα.</t>
         </is>
       </c>
       <c r="CF57" t="inlineStr">
         <is>
-          <t>https://valeri.gr/mallory-the-label-el</t>
+          <t>https://valeri.gr/ckontova-el</t>
         </is>
       </c>
       <c r="CH57" t="inlineStr">
         <is>
-          <t>MALLORY THE LABEL Buyers &amp; Greek Fashion Enthusiasts</t>
+          <t>CKONTOVA Buyers &amp; Greek Fashion Enthusiasts</t>
         </is>
       </c>
       <c r="EG57" t="inlineStr">
@@ -3877,7 +3617,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+          <t>CKONTOVA | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DV58" t="inlineStr">
@@ -3914,7 +3654,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+          <t>CKONTOVA | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DV59" t="inlineStr">
@@ -3951,12 +3691,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+          <t>CKONTOVA | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DV60" t="inlineStr">
         <is>
-          <t>* / Brand='mallory the label'</t>
+          <t>* / Brand='ckontova'</t>
         </is>
       </c>
       <c r="DX60" t="inlineStr">
@@ -3988,12 +3728,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+          <t>CKONTOVA | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY61" t="inlineStr">
         <is>
-          <t>mallory the label γυναικεία ρούχα</t>
+          <t>ckontova γυναικεία ρούχα</t>
         </is>
       </c>
       <c r="EG61" t="inlineStr">
@@ -4025,12 +3765,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+          <t>CKONTOVA | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY62" t="inlineStr">
         <is>
-          <t>mallory the label εκπτώσεις</t>
+          <t>ckontova εκπτώσεις</t>
         </is>
       </c>
       <c r="EG62" t="inlineStr">
@@ -4062,12 +3802,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+          <t>CKONTOVA | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY63" t="inlineStr">
         <is>
-          <t>mallory the label καλοκαιρινή συλλογή</t>
+          <t>ckontova καλοκαιρινή συλλογή</t>
         </is>
       </c>
       <c r="EG63" t="inlineStr">
@@ -4099,12 +3839,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+          <t>CKONTOVA | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY64" t="inlineStr">
         <is>
-          <t>mallory the label φόρεμα</t>
+          <t>ckontova φόρεμα</t>
         </is>
       </c>
       <c r="EG64" t="inlineStr">
@@ -4136,12 +3876,12 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+          <t>CKONTOVA | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY65" t="inlineStr">
         <is>
-          <t>mallory the label online</t>
+          <t>ckontova online</t>
         </is>
       </c>
       <c r="EG65" t="inlineStr">
@@ -4173,12 +3913,12 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+          <t>CKONTOVA | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY66" t="inlineStr">
         <is>
-          <t>αγορά mallory the label ρούχα</t>
+          <t>αγορά ckontova ρούχα</t>
         </is>
       </c>
       <c r="EG66" t="inlineStr">
@@ -4210,12 +3950,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+          <t>CKONTOVA | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY67" t="inlineStr">
         <is>
-          <t>mallory the label valeri</t>
+          <t>ckontova valeri</t>
         </is>
       </c>
       <c r="EG67" t="inlineStr">
@@ -4247,12 +3987,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+          <t>CKONTOVA | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY68" t="inlineStr">
         <is>
-          <t>mallory the label προσφορές</t>
+          <t>ckontova προσφορές</t>
         </is>
       </c>
       <c r="EG68" t="inlineStr">
@@ -4284,12 +4024,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+          <t>CKONTOVA | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY69" t="inlineStr">
         <is>
-          <t>mallory the label clothing sale</t>
+          <t>ckontova clothing sale</t>
         </is>
       </c>
       <c r="EG69" t="inlineStr">
@@ -4321,12 +4061,12 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+          <t>CKONTOVA | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY70" t="inlineStr">
         <is>
-          <t>mallory the label summer sale</t>
+          <t>ckontova summer sale</t>
         </is>
       </c>
       <c r="EG70" t="inlineStr">
@@ -4358,12 +4098,12 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+          <t>CKONTOVA | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY71" t="inlineStr">
         <is>
-          <t>buy mallory the label online</t>
+          <t>buy ckontova online</t>
         </is>
       </c>
       <c r="EG71" t="inlineStr">
@@ -4395,12 +4135,12 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+          <t>CKONTOVA | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY72" t="inlineStr">
         <is>
-          <t>mallory the label dresses</t>
+          <t>ckontova dresses</t>
         </is>
       </c>
       <c r="EG72" t="inlineStr">
@@ -4432,7 +4172,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+          <t>CKONTOVA | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY73" t="inlineStr">
@@ -4469,7 +4209,7 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+          <t>CKONTOVA | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY74" t="inlineStr">
@@ -4506,142 +4246,142 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+          <t>LA CHAINE | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>SALT AND PEPPER Summer Sale</t>
+          <t>LA CHAINE Summer Sale</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>SALT AND PEPPER -20%</t>
+          <t>LA CHAINE -20%</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>Shop SALT AND PEPPER Now</t>
+          <t>Shop LA CHAINE Now</t>
         </is>
       </c>
       <c r="AQ75" t="inlineStr">
         <is>
-          <t>SALT AND PEPPER σε Έκπτωση</t>
+          <t>LA CHAINE σε Έκπτωση</t>
         </is>
       </c>
       <c r="AR75" t="inlineStr">
         <is>
-          <t>SALT AND PEPPER | Valeri.gr</t>
+          <t>LA CHAINE | Valeri.gr</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>Έκπτωση -20% SALT AND PEPPER</t>
+          <t>LA CHAINE Καλοκαιρινή Μόδα</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>Έκπτωση -20% LA CHAINE</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>Καλοκαιρινές Εκπτώσεις</t>
         </is>
       </c>
-      <c r="AU75" t="inlineStr">
+      <c r="AV75" t="inlineStr">
         <is>
           <t>Δωρεάν Επιστροφές Πάντα</t>
         </is>
       </c>
-      <c r="AV75" t="inlineStr">
+      <c r="AW75" t="inlineStr">
         <is>
           <t>Παράδοση σε 2-3 Μέρες</t>
         </is>
       </c>
-      <c r="AW75" t="inlineStr">
+      <c r="AX75" t="inlineStr">
         <is>
           <t>Αγόρασε στο Valeri.gr</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
+      <c r="AY75" t="inlineStr">
         <is>
           <t>Γυναικεία Μόδα Ελλάδα</t>
         </is>
       </c>
-      <c r="AY75" t="inlineStr">
+      <c r="AZ75" t="inlineStr">
         <is>
           <t>Shop the Designer Sale</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
+      <c r="BA75" t="inlineStr">
         <is>
           <t>Your Summer Upgrade</t>
         </is>
       </c>
-      <c r="BA75" t="inlineStr">
+      <c r="BB75" t="inlineStr">
         <is>
           <t>Summer Sale Is Here</t>
         </is>
       </c>
-      <c r="BB75" t="inlineStr">
-        <is>
-          <t>Στυλάτα Γυναικεία Ρούχα</t>
-        </is>
-      </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>SALT AND PEPPER Summer Sale στο Valeri.gr – Εκπτώσεις -20% &amp; Δωρεάν Επιστροφές</t>
+          <t>LA CHAINE Summer Sale στο Valeri.gr – Εκπτώσεις -20% &amp; Δωρεάν Επιστροφές</t>
         </is>
       </c>
       <c r="BD75" t="inlineStr">
         <is>
-          <t>Shop the Designer Sale at Valeri.gr – SALT AND PEPPER -20% Off</t>
+          <t>Shop the Designer Sale at Valeri.gr – LA CHAINE -20% Off</t>
         </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
-          <t>Your summer wardrobe just got an upgrade – SALT AND PEPPER -20% στο Valeri.gr</t>
+          <t>Your summer wardrobe just got an upgrade – LA CHAINE -20% στο Valeri.gr</t>
         </is>
       </c>
       <c r="BF75" t="inlineStr">
         <is>
-          <t>Γυναικεία Μόδα SALT AND PEPPER σε Έκπτωση | Παράδοση 2-3 Μέρες σε όλη την Ελλάδα</t>
+          <t>Γυναικεία Μόδα LA CHAINE σε Έκπτωση | Παράδοση 2-3 Μέρες σε όλη την Ελλάδα</t>
         </is>
       </c>
       <c r="BG75" t="inlineStr">
         <is>
-          <t>Ανακάλυψε τη Συλλογή SALT AND PEPPER με έκπτωση -20% μόνο στο Valeri.gr</t>
+          <t>Ανακάλυψε τη Συλλογή LA CHAINE με έκπτωση -20% μόνο στο Valeri.gr</t>
         </is>
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>Ανακάλυψε τη συλλογή SALT AND PEPPER με έκπτωση -20%. Αγόρασε online στο Valeri.gr.</t>
+          <t>Ανακάλυψε τη συλλογή LA CHAINE με έκπτωση -20%. Αγόρασε online στο Valeri.gr.</t>
         </is>
       </c>
       <c r="BI75" t="inlineStr">
         <is>
-          <t>Shop the Designer Sale at Valeri.gr. SALT AND PEPPER -20% off. Free returns always.</t>
+          <t>Shop the Designer Sale at Valeri.gr. LA CHAINE -20% off. Free returns always.</t>
         </is>
       </c>
       <c r="BJ75" t="inlineStr">
         <is>
-          <t>Γυναικεία μόδα SALT AND PEPPER σε έκπτωση. Δωρεάν επιστροφές &amp; παράδοση 2-3 μέρες.</t>
+          <t>Γυναικεία μόδα LA CHAINE σε έκπτωση. Δωρεάν επιστροφές &amp; παράδοση 2-3 μέρες.</t>
         </is>
       </c>
       <c r="BK75" t="inlineStr">
         <is>
-          <t>Το καλοκαιρινό σου wardrobe αναβαθμίζεται. SALT AND PEPPER -20% μόνο στο Valeri.gr.</t>
+          <t>Το καλοκαιρινό σου wardrobe αναβαθμίζεται. LA CHAINE -20% μόνο στο Valeri.gr.</t>
         </is>
       </c>
       <c r="BL75" t="inlineStr">
         <is>
-          <t>Στυλάτα κομμάτια SALT AND PEPPER με έκπτωση. Παράδοση 2-3 μέρες σε όλη την Ελλάδα.</t>
+          <t>Στυλάτα κομμάτια LA CHAINE με έκπτωση. Παράδοση 2-3 μέρες σε όλη την Ελλάδα.</t>
         </is>
       </c>
       <c r="CF75" t="inlineStr">
         <is>
-          <t>https://valeri.gr/salt-and-pepper-el</t>
+          <t>https://valeri.gr/la-chaine-el</t>
         </is>
       </c>
       <c r="CH75" t="inlineStr">
         <is>
-          <t>SALT AND PEPPER Buyers &amp; Greek Fashion Enthusiasts</t>
+          <t>LA CHAINE Buyers &amp; Greek Fashion Enthusiasts</t>
         </is>
       </c>
       <c r="EG75" t="inlineStr">
@@ -4673,7 +4413,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+          <t>LA CHAINE | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DV76" t="inlineStr">
@@ -4710,7 +4450,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+          <t>LA CHAINE | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DV77" t="inlineStr">
@@ -4747,12 +4487,12 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+          <t>LA CHAINE | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DV78" t="inlineStr">
         <is>
-          <t>* / Brand='salt and pepper'</t>
+          <t>* / Brand='la chaine'</t>
         </is>
       </c>
       <c r="DX78" t="inlineStr">
@@ -4784,12 +4524,12 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+          <t>LA CHAINE | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY79" t="inlineStr">
         <is>
-          <t>salt and pepper γυναικεία ρούχα</t>
+          <t>la chaine γυναικεία ρούχα</t>
         </is>
       </c>
       <c r="EG79" t="inlineStr">
@@ -4821,12 +4561,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+          <t>LA CHAINE | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY80" t="inlineStr">
         <is>
-          <t>salt and pepper εκπτώσεις</t>
+          <t>la chaine εκπτώσεις</t>
         </is>
       </c>
       <c r="EG80" t="inlineStr">
@@ -4858,12 +4598,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+          <t>LA CHAINE | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY81" t="inlineStr">
         <is>
-          <t>salt and pepper καλοκαιρινή συλλογή</t>
+          <t>la chaine καλοκαιρινή συλλογή</t>
         </is>
       </c>
       <c r="EG81" t="inlineStr">
@@ -4895,12 +4635,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+          <t>LA CHAINE | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY82" t="inlineStr">
         <is>
-          <t>salt and pepper φόρεμα</t>
+          <t>la chaine φόρεμα</t>
         </is>
       </c>
       <c r="EG82" t="inlineStr">
@@ -4932,12 +4672,12 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+          <t>LA CHAINE | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY83" t="inlineStr">
         <is>
-          <t>salt and pepper online</t>
+          <t>la chaine online</t>
         </is>
       </c>
       <c r="EG83" t="inlineStr">
@@ -4969,12 +4709,12 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+          <t>LA CHAINE | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY84" t="inlineStr">
         <is>
-          <t>αγορά salt and pepper ρούχα</t>
+          <t>αγορά la chaine ρούχα</t>
         </is>
       </c>
       <c r="EG84" t="inlineStr">
@@ -5006,12 +4746,12 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+          <t>LA CHAINE | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY85" t="inlineStr">
         <is>
-          <t>salt and pepper valeri</t>
+          <t>la chaine valeri</t>
         </is>
       </c>
       <c r="EG85" t="inlineStr">
@@ -5043,12 +4783,12 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+          <t>LA CHAINE | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY86" t="inlineStr">
         <is>
-          <t>salt and pepper προσφορές</t>
+          <t>la chaine προσφορές</t>
         </is>
       </c>
       <c r="EG86" t="inlineStr">
@@ -5080,12 +4820,12 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+          <t>LA CHAINE | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY87" t="inlineStr">
         <is>
-          <t>salt and pepper clothing sale</t>
+          <t>la chaine clothing sale</t>
         </is>
       </c>
       <c r="EG87" t="inlineStr">
@@ -5117,12 +4857,12 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+          <t>LA CHAINE | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY88" t="inlineStr">
         <is>
-          <t>salt and pepper summer sale</t>
+          <t>la chaine summer sale</t>
         </is>
       </c>
       <c r="EG88" t="inlineStr">
@@ -5154,12 +4894,12 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+          <t>LA CHAINE | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY89" t="inlineStr">
         <is>
-          <t>buy salt and pepper online</t>
+          <t>buy la chaine online</t>
         </is>
       </c>
       <c r="EG89" t="inlineStr">
@@ -5191,12 +4931,12 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+          <t>LA CHAINE | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY90" t="inlineStr">
         <is>
-          <t>salt and pepper dresses</t>
+          <t>la chaine dresses</t>
         </is>
       </c>
       <c r="EG90" t="inlineStr">
@@ -5228,7 +4968,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+          <t>LA CHAINE | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY91" t="inlineStr">
@@ -5265,7 +5005,7 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+          <t>LA CHAINE | Summer Sales | BOFU</t>
         </is>
       </c>
       <c r="DY92" t="inlineStr">
@@ -5300,25 +5040,164 @@
           <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
         </is>
       </c>
-      <c r="CV93" t="n">
-        <v>2300</v>
-      </c>
-      <c r="CW93" t="inlineStr">
-        <is>
-          <t>Griechenland</t>
-        </is>
-      </c>
-      <c r="CX93" t="n">
-        <v>8520000</v>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="AN93" t="inlineStr">
+        <is>
+          <t>MALLORY THE LABEL Summer Sale</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>MALLORY THE LABEL -20%</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>Shop MALLORY THE LABEL Now</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>MALLORY THE LABEL σε Έκπτωση</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>MALLORY THE LABEL | Valeri.gr</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>Έκπτωση -20% MALLORY THE LABEL</t>
+        </is>
+      </c>
+      <c r="AT93" t="inlineStr">
+        <is>
+          <t>Καλοκαιρινές Εκπτώσεις</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>Δωρεάν Επιστροφές Πάντα</t>
+        </is>
+      </c>
+      <c r="AV93" t="inlineStr">
+        <is>
+          <t>Παράδοση σε 2-3 Μέρες</t>
+        </is>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Αγόρασε στο Valeri.gr</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Γυναικεία Μόδα Ελλάδα</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Shop the Designer Sale</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>Your Summer Upgrade</t>
+        </is>
+      </c>
+      <c r="BA93" t="inlineStr">
+        <is>
+          <t>Summer Sale Is Here</t>
+        </is>
+      </c>
+      <c r="BB93" t="inlineStr">
+        <is>
+          <t>Στυλάτα Γυναικεία Ρούχα</t>
+        </is>
+      </c>
+      <c r="BC93" t="inlineStr">
+        <is>
+          <t>MALLORY THE LABEL Summer Sale στο Valeri.gr – Εκπτώσεις -20% &amp; Δωρεάν Επιστροφές</t>
+        </is>
+      </c>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>Shop the Designer Sale at Valeri.gr – MALLORY THE LABEL -20% Off</t>
+        </is>
+      </c>
+      <c r="BE93" t="inlineStr">
+        <is>
+          <t>Your summer wardrobe just got an upgrade – MALLORY THE LABEL -20% στο Valeri.gr</t>
+        </is>
+      </c>
+      <c r="BF93" t="inlineStr">
+        <is>
+          <t>Γυναικεία Μόδα MALLORY THE LABEL σε Έκπτωση | Παράδοση 2-3 Μέρες σε όλη την Ελλάδα</t>
+        </is>
+      </c>
+      <c r="BG93" t="inlineStr">
+        <is>
+          <t>Ανακάλυψε τη Συλλογή MALLORY THE LABEL με έκπτωση -20% μόνο στο Valeri.gr</t>
+        </is>
+      </c>
+      <c r="BH93" t="inlineStr">
+        <is>
+          <t>Ανακάλυψε τη συλλογή MALLORY THE LABEL με έκπτωση -20%. Αγόρασε online στο Valeri.gr.</t>
+        </is>
+      </c>
+      <c r="BI93" t="inlineStr">
+        <is>
+          <t>Shop the Designer Sale at Valeri.gr. MALLORY THE LABEL -20% off. Free returns always.</t>
+        </is>
+      </c>
+      <c r="BJ93" t="inlineStr">
+        <is>
+          <t>Γυναικεία μόδα MALLORY THE LABEL σε έκπτωση. Δωρεάν επιστροφές &amp; παράδοση 2-3 μέρες.</t>
+        </is>
+      </c>
+      <c r="BK93" t="inlineStr">
+        <is>
+          <t>Το καλοκαιρινό σου wardrobe αναβαθμίζεται. MALLORY THE LABEL -20% μόνο στο Valeri.gr.</t>
+        </is>
+      </c>
+      <c r="BL93" t="inlineStr">
+        <is>
+          <t>Στυλάτα κομμάτια MALLORY THE LABEL με έκπτωση. Παράδοση 2-3 μέρες σε όλη την Ελλάδα.</t>
+        </is>
+      </c>
+      <c r="CF93" t="inlineStr">
+        <is>
+          <t>https://valeri.gr/mallory-the-label-el</t>
+        </is>
+      </c>
+      <c r="CH93" t="inlineStr">
+        <is>
+          <t>MALLORY THE LABEL Buyers &amp; Greek Fashion Enthusiasts</t>
+        </is>
       </c>
       <c r="EG93" t="inlineStr">
         <is>
           <t>Enabled</t>
         </is>
       </c>
-      <c r="EJ93" t="inlineStr">
-        <is>
-          <t>Enabled</t>
+      <c r="EI93" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK93" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="EL93" t="inlineStr">
+        <is>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -5328,65 +5207,19 @@
           <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="CF94" t="inlineStr">
-        <is>
-          <t>https://valeri.gr/arpyes-el</t>
-        </is>
-      </c>
-      <c r="DC94" t="inlineStr">
-        <is>
-          <t>ARPYES</t>
-        </is>
-      </c>
-      <c r="DE94" t="inlineStr">
-        <is>
-          <t>el</t>
-        </is>
-      </c>
-      <c r="DI94" t="inlineStr">
-        <is>
-          <t>30.00%</t>
-        </is>
-      </c>
-      <c r="DL94" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="DO94" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="DP94" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="DS94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DT94" t="inlineStr">
-        <is>
-          <t>Advertiser</t>
-        </is>
-      </c>
-      <c r="DU94" t="inlineStr">
-        <is>
-          <t>Advertiser</t>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DV94" t="inlineStr">
+        <is>
+          <t>* /</t>
+        </is>
+      </c>
+      <c r="DX94" t="inlineStr">
+        <is>
+          <t>Subdivision</t>
         </is>
       </c>
       <c r="EG94" t="inlineStr">
@@ -5394,14 +5227,14 @@
           <t>Enabled</t>
         </is>
       </c>
+      <c r="EI94" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
       <c r="EJ94" t="inlineStr">
         <is>
           <t>Enabled</t>
-        </is>
-      </c>
-      <c r="EK94" t="inlineStr">
-        <is>
-          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -5411,65 +5244,19 @@
           <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="CF95" t="inlineStr">
-        <is>
-          <t>https://valeri.gr/ckontova-el</t>
-        </is>
-      </c>
-      <c r="DC95" t="inlineStr">
-        <is>
-          <t>CKONTOVA</t>
-        </is>
-      </c>
-      <c r="DE95" t="inlineStr">
-        <is>
-          <t>el</t>
-        </is>
-      </c>
-      <c r="DI95" t="inlineStr">
-        <is>
-          <t>20.00%</t>
-        </is>
-      </c>
-      <c r="DL95" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="DO95" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="DP95" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="DS95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DT95" t="inlineStr">
-        <is>
-          <t>Advertiser</t>
-        </is>
-      </c>
-      <c r="DU95" t="inlineStr">
-        <is>
-          <t>Advertiser</t>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DV95" t="inlineStr">
+        <is>
+          <t>* / Brand=*</t>
+        </is>
+      </c>
+      <c r="DX95" t="inlineStr">
+        <is>
+          <t>Excluded</t>
         </is>
       </c>
       <c r="EG95" t="inlineStr">
@@ -5477,14 +5264,14 @@
           <t>Enabled</t>
         </is>
       </c>
+      <c r="EI95" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
       <c r="EJ95" t="inlineStr">
         <is>
           <t>Enabled</t>
-        </is>
-      </c>
-      <c r="EK95" t="inlineStr">
-        <is>
-          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -5494,65 +5281,19 @@
           <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="CF96" t="inlineStr">
-        <is>
-          <t>https://valeri.gr/la-chaine-el</t>
-        </is>
-      </c>
-      <c r="DC96" t="inlineStr">
-        <is>
-          <t>LA CHAINE</t>
-        </is>
-      </c>
-      <c r="DE96" t="inlineStr">
-        <is>
-          <t>el</t>
-        </is>
-      </c>
-      <c r="DI96" t="inlineStr">
-        <is>
-          <t>20.00%</t>
-        </is>
-      </c>
-      <c r="DL96" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="DO96" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="DP96" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="DS96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DT96" t="inlineStr">
-        <is>
-          <t>Advertiser</t>
-        </is>
-      </c>
-      <c r="DU96" t="inlineStr">
-        <is>
-          <t>Advertiser</t>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DV96" t="inlineStr">
+        <is>
+          <t>* / Brand='mallory the label'</t>
+        </is>
+      </c>
+      <c r="DX96" t="inlineStr">
+        <is>
+          <t>Biddable</t>
         </is>
       </c>
       <c r="EG96" t="inlineStr">
@@ -5560,14 +5301,14 @@
           <t>Enabled</t>
         </is>
       </c>
+      <c r="EI96" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
       <c r="EJ96" t="inlineStr">
         <is>
           <t>Enabled</t>
-        </is>
-      </c>
-      <c r="EK96" t="inlineStr">
-        <is>
-          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -5577,68 +5318,22 @@
           <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="CF97" t="inlineStr">
-        <is>
-          <t>https://valeri.gr/mallory-the-label-el</t>
-        </is>
-      </c>
-      <c r="DC97" t="inlineStr">
-        <is>
-          <t>MALLORY THE LABEL</t>
-        </is>
-      </c>
-      <c r="DE97" t="inlineStr">
-        <is>
-          <t>el</t>
-        </is>
-      </c>
-      <c r="DI97" t="inlineStr">
-        <is>
-          <t>20.00%</t>
-        </is>
-      </c>
-      <c r="DL97" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="DO97" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="DP97" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="DS97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DT97" t="inlineStr">
-        <is>
-          <t>Advertiser</t>
-        </is>
-      </c>
-      <c r="DU97" t="inlineStr">
-        <is>
-          <t>Advertiser</t>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY97" t="inlineStr">
+        <is>
+          <t>mallory the label γυναικεία ρούχα</t>
         </is>
       </c>
       <c r="EG97" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI97" t="inlineStr">
         <is>
           <t>Enabled</t>
         </is>
@@ -5660,68 +5355,22 @@
           <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="CF98" t="inlineStr">
-        <is>
-          <t>https://valeri.gr/salt-and-pepper-el</t>
-        </is>
-      </c>
-      <c r="DC98" t="inlineStr">
-        <is>
-          <t>SALT AND PEPPER</t>
-        </is>
-      </c>
-      <c r="DE98" t="inlineStr">
-        <is>
-          <t>el</t>
-        </is>
-      </c>
-      <c r="DI98" t="inlineStr">
-        <is>
-          <t>20.00%</t>
-        </is>
-      </c>
-      <c r="DL98" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="DO98" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="DP98" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="DS98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DT98" t="inlineStr">
-        <is>
-          <t>Advertiser</t>
-        </is>
-      </c>
-      <c r="DU98" t="inlineStr">
-        <is>
-          <t>Advertiser</t>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY98" t="inlineStr">
+        <is>
+          <t>mallory the label εκπτώσεις</t>
         </is>
       </c>
       <c r="EG98" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI98" t="inlineStr">
         <is>
           <t>Enabled</t>
         </is>
@@ -5743,57 +5392,22 @@
           <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="CF99" t="inlineStr">
-        <is>
-          <t>https://valeri.gr/arpyes-el</t>
-        </is>
-      </c>
-      <c r="DS99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DT99" t="inlineStr">
-        <is>
-          <t>Advertiser</t>
-        </is>
-      </c>
-      <c r="DU99" t="inlineStr">
-        <is>
-          <t>Advertiser</t>
-        </is>
-      </c>
-      <c r="EA99" t="inlineStr">
-        <is>
-          <t>ARPYES έως -30%</t>
-        </is>
-      </c>
-      <c r="EB99" t="inlineStr">
-        <is>
-          <t>Καλοκαιρινές εκπτώσεις</t>
-        </is>
-      </c>
-      <c r="EC99" t="inlineStr">
-        <is>
-          <t>Αγόρασε τώρα</t>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY99" t="inlineStr">
+        <is>
+          <t>mallory the label καλοκαιρινή συλλογή</t>
         </is>
       </c>
       <c r="EG99" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI99" t="inlineStr">
         <is>
           <t>Enabled</t>
         </is>
@@ -5815,57 +5429,22 @@
           <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="CF100" t="inlineStr">
-        <is>
-          <t>https://valeri.gr/ckontova-el</t>
-        </is>
-      </c>
-      <c r="DS100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DT100" t="inlineStr">
-        <is>
-          <t>Advertiser</t>
-        </is>
-      </c>
-      <c r="DU100" t="inlineStr">
-        <is>
-          <t>Advertiser</t>
-        </is>
-      </c>
-      <c r="EA100" t="inlineStr">
-        <is>
-          <t>CKONTOVA -20%</t>
-        </is>
-      </c>
-      <c r="EB100" t="inlineStr">
-        <is>
-          <t>Γυναικεία μόδα σε έκπτωση</t>
-        </is>
-      </c>
-      <c r="EC100" t="inlineStr">
-        <is>
-          <t>Δες τη συλλογή</t>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY100" t="inlineStr">
+        <is>
+          <t>mallory the label φόρεμα</t>
         </is>
       </c>
       <c r="EG100" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI100" t="inlineStr">
         <is>
           <t>Enabled</t>
         </is>
@@ -5887,57 +5466,22 @@
           <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="CF101" t="inlineStr">
-        <is>
-          <t>https://valeri.gr/la-chaine-el</t>
-        </is>
-      </c>
-      <c r="DS101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DT101" t="inlineStr">
-        <is>
-          <t>Advertiser</t>
-        </is>
-      </c>
-      <c r="DU101" t="inlineStr">
-        <is>
-          <t>Advertiser</t>
-        </is>
-      </c>
-      <c r="EA101" t="inlineStr">
-        <is>
-          <t>LA CHAINE -20%</t>
-        </is>
-      </c>
-      <c r="EB101" t="inlineStr">
-        <is>
-          <t>Minimal &amp; chic κομμάτια</t>
-        </is>
-      </c>
-      <c r="EC101" t="inlineStr">
-        <is>
-          <t>Αγόρασε online</t>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY101" t="inlineStr">
+        <is>
+          <t>mallory the label online</t>
         </is>
       </c>
       <c r="EG101" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI101" t="inlineStr">
         <is>
           <t>Enabled</t>
         </is>
@@ -5959,57 +5503,22 @@
           <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="CF102" t="inlineStr">
-        <is>
-          <t>https://valeri.gr/mallory-the-label-el</t>
-        </is>
-      </c>
-      <c r="DS102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DT102" t="inlineStr">
-        <is>
-          <t>Advertiser</t>
-        </is>
-      </c>
-      <c r="DU102" t="inlineStr">
-        <is>
-          <t>Advertiser</t>
-        </is>
-      </c>
-      <c r="EA102" t="inlineStr">
-        <is>
-          <t>MALLORY THE LABEL -20%</t>
-        </is>
-      </c>
-      <c r="EB102" t="inlineStr">
-        <is>
-          <t>Mediterranean elegance</t>
-        </is>
-      </c>
-      <c r="EC102" t="inlineStr">
-        <is>
-          <t>Νέα συλλογή</t>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY102" t="inlineStr">
+        <is>
+          <t>αγορά mallory the label ρούχα</t>
         </is>
       </c>
       <c r="EG102" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI102" t="inlineStr">
         <is>
           <t>Enabled</t>
         </is>
@@ -6031,57 +5540,22 @@
           <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="CF103" t="inlineStr">
-        <is>
-          <t>https://valeri.gr/salt-and-pepper-el</t>
-        </is>
-      </c>
-      <c r="DS103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DT103" t="inlineStr">
-        <is>
-          <t>Advertiser</t>
-        </is>
-      </c>
-      <c r="DU103" t="inlineStr">
-        <is>
-          <t>Advertiser</t>
-        </is>
-      </c>
-      <c r="EA103" t="inlineStr">
-        <is>
-          <t>SALT AND PEPPER -20%</t>
-        </is>
-      </c>
-      <c r="EB103" t="inlineStr">
-        <is>
-          <t>Handmade denim από Ελλάδα</t>
-        </is>
-      </c>
-      <c r="EC103" t="inlineStr">
-        <is>
-          <t>Δες τα τζιν</t>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY103" t="inlineStr">
+        <is>
+          <t>mallory the label valeri</t>
         </is>
       </c>
       <c r="EG103" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI103" t="inlineStr">
         <is>
           <t>Enabled</t>
         </is>
@@ -6103,57 +5577,22 @@
           <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="CF104" t="inlineStr">
-        <is>
-          <t>https://valeri.gr/sales-el</t>
-        </is>
-      </c>
-      <c r="DS104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DT104" t="inlineStr">
-        <is>
-          <t>Advertiser</t>
-        </is>
-      </c>
-      <c r="DU104" t="inlineStr">
-        <is>
-          <t>Advertiser</t>
-        </is>
-      </c>
-      <c r="EA104" t="inlineStr">
-        <is>
-          <t>Όλες οι Εκπτώσεις</t>
-        </is>
-      </c>
-      <c r="EB104" t="inlineStr">
-        <is>
-          <t>Shop the Designer Sale</t>
-        </is>
-      </c>
-      <c r="EC104" t="inlineStr">
-        <is>
-          <t>Έως -30%</t>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY104" t="inlineStr">
+        <is>
+          <t>mallory the label προσφορές</t>
         </is>
       </c>
       <c r="EG104" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI104" t="inlineStr">
         <is>
           <t>Enabled</t>
         </is>
@@ -6175,57 +5614,22 @@
           <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="O105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="CF105" t="inlineStr">
-        <is>
-          <t>https://valeri.gr/new-arrivals-el</t>
-        </is>
-      </c>
-      <c r="DS105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DT105" t="inlineStr">
-        <is>
-          <t>Advertiser</t>
-        </is>
-      </c>
-      <c r="DU105" t="inlineStr">
-        <is>
-          <t>Advertiser</t>
-        </is>
-      </c>
-      <c r="EA105" t="inlineStr">
-        <is>
-          <t>Νέες Αφίξεις</t>
-        </is>
-      </c>
-      <c r="EB105" t="inlineStr">
-        <is>
-          <t>Ανακάλυψε τα νέα κομμάτια</t>
-        </is>
-      </c>
-      <c r="EC105" t="inlineStr">
-        <is>
-          <t>Καλοκαίρι 2026</t>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY105" t="inlineStr">
+        <is>
+          <t>mallory the label clothing sale</t>
         </is>
       </c>
       <c r="EG105" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI105" t="inlineStr">
         <is>
           <t>Enabled</t>
         </is>
@@ -6247,27 +5651,1955 @@
           <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
         </is>
       </c>
-      <c r="DS106" t="inlineStr">
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY106" t="inlineStr">
+        <is>
+          <t>mallory the label summer sale</t>
+        </is>
+      </c>
+      <c r="EG106" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI106" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ106" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK106" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY107" t="inlineStr">
+        <is>
+          <t>buy mallory the label online</t>
+        </is>
+      </c>
+      <c r="EG107" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI107" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ107" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK107" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY108" t="inlineStr">
+        <is>
+          <t>mallory the label dresses</t>
+        </is>
+      </c>
+      <c r="EG108" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI108" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ108" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK108" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY109" t="inlineStr">
+        <is>
+          <t>designer sale γυναικεία ρούχα</t>
+        </is>
+      </c>
+      <c r="EG109" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI109" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ109" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK109" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>MALLORY THE LABEL | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY110" t="inlineStr">
+        <is>
+          <t>επώνυμα ρούχα εκπτώσεις</t>
+        </is>
+      </c>
+      <c r="EG110" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI110" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ110" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK110" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="AN111" t="inlineStr">
+        <is>
+          <t>SALT AND PEPPER Summer Sale</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>SALT AND PEPPER -20%</t>
+        </is>
+      </c>
+      <c r="AP111" t="inlineStr">
+        <is>
+          <t>Shop SALT AND PEPPER Now</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>SALT AND PEPPER σε Έκπτωση</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>SALT AND PEPPER | Valeri.gr</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>Έκπτωση -20% SALT AND PEPPER</t>
+        </is>
+      </c>
+      <c r="AT111" t="inlineStr">
+        <is>
+          <t>Καλοκαιρινές Εκπτώσεις</t>
+        </is>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>Δωρεάν Επιστροφές Πάντα</t>
+        </is>
+      </c>
+      <c r="AV111" t="inlineStr">
+        <is>
+          <t>Παράδοση σε 2-3 Μέρες</t>
+        </is>
+      </c>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Αγόρασε στο Valeri.gr</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Γυναικεία Μόδα Ελλάδα</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>Shop the Designer Sale</t>
+        </is>
+      </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>Your Summer Upgrade</t>
+        </is>
+      </c>
+      <c r="BA111" t="inlineStr">
+        <is>
+          <t>Summer Sale Is Here</t>
+        </is>
+      </c>
+      <c r="BB111" t="inlineStr">
+        <is>
+          <t>Στυλάτα Γυναικεία Ρούχα</t>
+        </is>
+      </c>
+      <c r="BC111" t="inlineStr">
+        <is>
+          <t>SALT AND PEPPER Summer Sale στο Valeri.gr – Εκπτώσεις -20% &amp; Δωρεάν Επιστροφές</t>
+        </is>
+      </c>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>Shop the Designer Sale at Valeri.gr – SALT AND PEPPER -20% Off</t>
+        </is>
+      </c>
+      <c r="BE111" t="inlineStr">
+        <is>
+          <t>Your summer wardrobe just got an upgrade – SALT AND PEPPER -20% στο Valeri.gr</t>
+        </is>
+      </c>
+      <c r="BF111" t="inlineStr">
+        <is>
+          <t>Γυναικεία Μόδα SALT AND PEPPER σε Έκπτωση | Παράδοση 2-3 Μέρες σε όλη την Ελλάδα</t>
+        </is>
+      </c>
+      <c r="BG111" t="inlineStr">
+        <is>
+          <t>Ανακάλυψε τη Συλλογή SALT AND PEPPER με έκπτωση -20% μόνο στο Valeri.gr</t>
+        </is>
+      </c>
+      <c r="BH111" t="inlineStr">
+        <is>
+          <t>Ανακάλυψε τη συλλογή SALT AND PEPPER με έκπτωση -20%. Αγόρασε online στο Valeri.gr.</t>
+        </is>
+      </c>
+      <c r="BI111" t="inlineStr">
+        <is>
+          <t>Shop the Designer Sale at Valeri.gr. SALT AND PEPPER -20% off. Free returns always.</t>
+        </is>
+      </c>
+      <c r="BJ111" t="inlineStr">
+        <is>
+          <t>Γυναικεία μόδα SALT AND PEPPER σε έκπτωση. Δωρεάν επιστροφές &amp; παράδοση 2-3 μέρες.</t>
+        </is>
+      </c>
+      <c r="BK111" t="inlineStr">
+        <is>
+          <t>Το καλοκαιρινό σου wardrobe αναβαθμίζεται. SALT AND PEPPER -20% μόνο στο Valeri.gr.</t>
+        </is>
+      </c>
+      <c r="BL111" t="inlineStr">
+        <is>
+          <t>Στυλάτα κομμάτια SALT AND PEPPER με έκπτωση. Παράδοση 2-3 μέρες σε όλη την Ελλάδα.</t>
+        </is>
+      </c>
+      <c r="CF111" t="inlineStr">
+        <is>
+          <t>https://valeri.gr/salt-and-pepper-el</t>
+        </is>
+      </c>
+      <c r="CH111" t="inlineStr">
+        <is>
+          <t>SALT AND PEPPER Buyers &amp; Greek Fashion Enthusiasts</t>
+        </is>
+      </c>
+      <c r="EG111" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI111" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK111" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="EL111" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DV112" t="inlineStr">
+        <is>
+          <t>* /</t>
+        </is>
+      </c>
+      <c r="DX112" t="inlineStr">
+        <is>
+          <t>Subdivision</t>
+        </is>
+      </c>
+      <c r="EG112" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI112" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ112" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DV113" t="inlineStr">
+        <is>
+          <t>* / Brand=*</t>
+        </is>
+      </c>
+      <c r="DX113" t="inlineStr">
+        <is>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="EG113" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI113" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ113" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DV114" t="inlineStr">
+        <is>
+          <t>* / Brand='salt and pepper'</t>
+        </is>
+      </c>
+      <c r="DX114" t="inlineStr">
+        <is>
+          <t>Biddable</t>
+        </is>
+      </c>
+      <c r="EG114" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI114" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ114" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY115" t="inlineStr">
+        <is>
+          <t>salt and pepper γυναικεία ρούχα</t>
+        </is>
+      </c>
+      <c r="EG115" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI115" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ115" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK115" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY116" t="inlineStr">
+        <is>
+          <t>salt and pepper εκπτώσεις</t>
+        </is>
+      </c>
+      <c r="EG116" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI116" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ116" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK116" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY117" t="inlineStr">
+        <is>
+          <t>salt and pepper καλοκαιρινή συλλογή</t>
+        </is>
+      </c>
+      <c r="EG117" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI117" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ117" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK117" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY118" t="inlineStr">
+        <is>
+          <t>salt and pepper φόρεμα</t>
+        </is>
+      </c>
+      <c r="EG118" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI118" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ118" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK118" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY119" t="inlineStr">
+        <is>
+          <t>salt and pepper online</t>
+        </is>
+      </c>
+      <c r="EG119" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI119" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ119" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK119" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY120" t="inlineStr">
+        <is>
+          <t>αγορά salt and pepper ρούχα</t>
+        </is>
+      </c>
+      <c r="EG120" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI120" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ120" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK120" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY121" t="inlineStr">
+        <is>
+          <t>salt and pepper valeri</t>
+        </is>
+      </c>
+      <c r="EG121" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI121" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ121" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK121" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY122" t="inlineStr">
+        <is>
+          <t>salt and pepper προσφορές</t>
+        </is>
+      </c>
+      <c r="EG122" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI122" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ122" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK122" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY123" t="inlineStr">
+        <is>
+          <t>salt and pepper clothing sale</t>
+        </is>
+      </c>
+      <c r="EG123" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI123" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ123" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK123" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY124" t="inlineStr">
+        <is>
+          <t>salt and pepper summer sale</t>
+        </is>
+      </c>
+      <c r="EG124" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI124" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ124" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK124" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY125" t="inlineStr">
+        <is>
+          <t>buy salt and pepper online</t>
+        </is>
+      </c>
+      <c r="EG125" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI125" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ125" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK125" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY126" t="inlineStr">
+        <is>
+          <t>salt and pepper dresses</t>
+        </is>
+      </c>
+      <c r="EG126" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI126" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ126" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK126" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY127" t="inlineStr">
+        <is>
+          <t>designer sale γυναικεία ρούχα</t>
+        </is>
+      </c>
+      <c r="EG127" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI127" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ127" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK127" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="AM128" t="inlineStr">
+        <is>
+          <t>SALT AND PEPPER | Summer Sales | BOFU</t>
+        </is>
+      </c>
+      <c r="DY128" t="inlineStr">
+        <is>
+          <t>επώνυμα ρούχα εκπτώσεις</t>
+        </is>
+      </c>
+      <c r="EG128" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EI128" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ128" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK128" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="CV129" t="n">
+        <v>2300</v>
+      </c>
+      <c r="CW129" t="inlineStr">
+        <is>
+          <t>Griechenland</t>
+        </is>
+      </c>
+      <c r="CX129" t="n">
+        <v>8520000</v>
+      </c>
+      <c r="EG129" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ129" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DT106" t="inlineStr">
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CF130" t="inlineStr">
+        <is>
+          <t>https://valeri.gr/arpyes-el</t>
+        </is>
+      </c>
+      <c r="DC130" t="inlineStr">
+        <is>
+          <t>ARPYES</t>
+        </is>
+      </c>
+      <c r="DE130" t="inlineStr">
+        <is>
+          <t>el</t>
+        </is>
+      </c>
+      <c r="DI130" t="inlineStr">
+        <is>
+          <t>30.00%</t>
+        </is>
+      </c>
+      <c r="DL130" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="DO130" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="DP130" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="DS130" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DT130" t="inlineStr">
         <is>
           <t>Advertiser</t>
         </is>
       </c>
-      <c r="DU106" t="inlineStr">
+      <c r="DU130" t="inlineStr">
         <is>
           <t>Advertiser</t>
         </is>
       </c>
-      <c r="ED106" t="inlineStr">
+      <c r="EG130" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ130" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK130" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CF131" t="inlineStr">
+        <is>
+          <t>https://valeri.gr/ckontova-el</t>
+        </is>
+      </c>
+      <c r="DC131" t="inlineStr">
+        <is>
+          <t>CKONTOVA</t>
+        </is>
+      </c>
+      <c r="DE131" t="inlineStr">
+        <is>
+          <t>el</t>
+        </is>
+      </c>
+      <c r="DI131" t="inlineStr">
+        <is>
+          <t>20.00%</t>
+        </is>
+      </c>
+      <c r="DL131" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="DO131" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="DP131" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="DS131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DT131" t="inlineStr">
+        <is>
+          <t>Advertiser</t>
+        </is>
+      </c>
+      <c r="DU131" t="inlineStr">
+        <is>
+          <t>Advertiser</t>
+        </is>
+      </c>
+      <c r="EG131" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ131" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK131" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CF132" t="inlineStr">
+        <is>
+          <t>https://valeri.gr/la-chaine-el</t>
+        </is>
+      </c>
+      <c r="DC132" t="inlineStr">
+        <is>
+          <t>LA CHAINE</t>
+        </is>
+      </c>
+      <c r="DE132" t="inlineStr">
+        <is>
+          <t>el</t>
+        </is>
+      </c>
+      <c r="DI132" t="inlineStr">
+        <is>
+          <t>20.00%</t>
+        </is>
+      </c>
+      <c r="DL132" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="DO132" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="DP132" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="DS132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DT132" t="inlineStr">
+        <is>
+          <t>Advertiser</t>
+        </is>
+      </c>
+      <c r="DU132" t="inlineStr">
+        <is>
+          <t>Advertiser</t>
+        </is>
+      </c>
+      <c r="EG132" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ132" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK132" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CF133" t="inlineStr">
+        <is>
+          <t>https://valeri.gr/mallory-the-label-el</t>
+        </is>
+      </c>
+      <c r="DC133" t="inlineStr">
+        <is>
+          <t>MALLORY THE LABEL</t>
+        </is>
+      </c>
+      <c r="DE133" t="inlineStr">
+        <is>
+          <t>el</t>
+        </is>
+      </c>
+      <c r="DI133" t="inlineStr">
+        <is>
+          <t>20.00%</t>
+        </is>
+      </c>
+      <c r="DL133" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="DO133" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="DP133" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="DS133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DT133" t="inlineStr">
+        <is>
+          <t>Advertiser</t>
+        </is>
+      </c>
+      <c r="DU133" t="inlineStr">
+        <is>
+          <t>Advertiser</t>
+        </is>
+      </c>
+      <c r="EG133" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ133" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK133" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CF134" t="inlineStr">
+        <is>
+          <t>https://valeri.gr/salt-and-pepper-el</t>
+        </is>
+      </c>
+      <c r="DC134" t="inlineStr">
+        <is>
+          <t>SALT AND PEPPER</t>
+        </is>
+      </c>
+      <c r="DE134" t="inlineStr">
+        <is>
+          <t>el</t>
+        </is>
+      </c>
+      <c r="DI134" t="inlineStr">
+        <is>
+          <t>20.00%</t>
+        </is>
+      </c>
+      <c r="DL134" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="DO134" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="DP134" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="DS134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DT134" t="inlineStr">
+        <is>
+          <t>Advertiser</t>
+        </is>
+      </c>
+      <c r="DU134" t="inlineStr">
+        <is>
+          <t>Advertiser</t>
+        </is>
+      </c>
+      <c r="EG134" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ134" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK134" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CF135" t="inlineStr">
+        <is>
+          <t>https://valeri.gr/arpyes-el</t>
+        </is>
+      </c>
+      <c r="DS135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DT135" t="inlineStr">
+        <is>
+          <t>Advertiser</t>
+        </is>
+      </c>
+      <c r="DU135" t="inlineStr">
+        <is>
+          <t>Advertiser</t>
+        </is>
+      </c>
+      <c r="EA135" t="inlineStr">
+        <is>
+          <t>ARPYES έως -30%</t>
+        </is>
+      </c>
+      <c r="EB135" t="inlineStr">
+        <is>
+          <t>Καλοκαιρινές εκπτώσεις</t>
+        </is>
+      </c>
+      <c r="EC135" t="inlineStr">
+        <is>
+          <t>Αγόρασε τώρα</t>
+        </is>
+      </c>
+      <c r="EG135" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ135" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK135" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CF136" t="inlineStr">
+        <is>
+          <t>https://valeri.gr/ckontova-el</t>
+        </is>
+      </c>
+      <c r="DS136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DT136" t="inlineStr">
+        <is>
+          <t>Advertiser</t>
+        </is>
+      </c>
+      <c r="DU136" t="inlineStr">
+        <is>
+          <t>Advertiser</t>
+        </is>
+      </c>
+      <c r="EA136" t="inlineStr">
+        <is>
+          <t>CKONTOVA -20%</t>
+        </is>
+      </c>
+      <c r="EB136" t="inlineStr">
+        <is>
+          <t>Γυναικεία μόδα σε έκπτωση</t>
+        </is>
+      </c>
+      <c r="EC136" t="inlineStr">
+        <is>
+          <t>Δες τη συλλογή</t>
+        </is>
+      </c>
+      <c r="EG136" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ136" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK136" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CF137" t="inlineStr">
+        <is>
+          <t>https://valeri.gr/la-chaine-el</t>
+        </is>
+      </c>
+      <c r="DS137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DT137" t="inlineStr">
+        <is>
+          <t>Advertiser</t>
+        </is>
+      </c>
+      <c r="DU137" t="inlineStr">
+        <is>
+          <t>Advertiser</t>
+        </is>
+      </c>
+      <c r="EA137" t="inlineStr">
+        <is>
+          <t>LA CHAINE -20%</t>
+        </is>
+      </c>
+      <c r="EB137" t="inlineStr">
+        <is>
+          <t>Minimal &amp; chic κομμάτια</t>
+        </is>
+      </c>
+      <c r="EC137" t="inlineStr">
+        <is>
+          <t>Αγόρασε online</t>
+        </is>
+      </c>
+      <c r="EG137" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ137" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK137" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CF138" t="inlineStr">
+        <is>
+          <t>https://valeri.gr/mallory-the-label-el</t>
+        </is>
+      </c>
+      <c r="DS138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DT138" t="inlineStr">
+        <is>
+          <t>Advertiser</t>
+        </is>
+      </c>
+      <c r="DU138" t="inlineStr">
+        <is>
+          <t>Advertiser</t>
+        </is>
+      </c>
+      <c r="EA138" t="inlineStr">
+        <is>
+          <t>MALLORY THE LABEL -20%</t>
+        </is>
+      </c>
+      <c r="EB138" t="inlineStr">
+        <is>
+          <t>Mediterranean elegance</t>
+        </is>
+      </c>
+      <c r="EC138" t="inlineStr">
+        <is>
+          <t>Νέα συλλογή</t>
+        </is>
+      </c>
+      <c r="EG138" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ138" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK138" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CF139" t="inlineStr">
+        <is>
+          <t>https://valeri.gr/salt-and-pepper-el</t>
+        </is>
+      </c>
+      <c r="DS139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DT139" t="inlineStr">
+        <is>
+          <t>Advertiser</t>
+        </is>
+      </c>
+      <c r="DU139" t="inlineStr">
+        <is>
+          <t>Advertiser</t>
+        </is>
+      </c>
+      <c r="EA139" t="inlineStr">
+        <is>
+          <t>SALT AND PEPPER -20%</t>
+        </is>
+      </c>
+      <c r="EB139" t="inlineStr">
+        <is>
+          <t>Handmade denim από Ελλάδα</t>
+        </is>
+      </c>
+      <c r="EC139" t="inlineStr">
+        <is>
+          <t>Δες τα τζιν</t>
+        </is>
+      </c>
+      <c r="EG139" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ139" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK139" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CF140" t="inlineStr">
+        <is>
+          <t>https://valeri.gr/sales-el</t>
+        </is>
+      </c>
+      <c r="DS140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DT140" t="inlineStr">
+        <is>
+          <t>Advertiser</t>
+        </is>
+      </c>
+      <c r="DU140" t="inlineStr">
+        <is>
+          <t>Advertiser</t>
+        </is>
+      </c>
+      <c r="EA140" t="inlineStr">
+        <is>
+          <t>Όλες οι Εκπτώσεις</t>
+        </is>
+      </c>
+      <c r="EB140" t="inlineStr">
+        <is>
+          <t>Shop the Designer Sale</t>
+        </is>
+      </c>
+      <c r="EC140" t="inlineStr">
+        <is>
+          <t>Έως -30%</t>
+        </is>
+      </c>
+      <c r="EG140" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ140" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK140" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CF141" t="inlineStr">
+        <is>
+          <t>https://valeri.gr/new-arrivals-el</t>
+        </is>
+      </c>
+      <c r="DS141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DT141" t="inlineStr">
+        <is>
+          <t>Advertiser</t>
+        </is>
+      </c>
+      <c r="DU141" t="inlineStr">
+        <is>
+          <t>Advertiser</t>
+        </is>
+      </c>
+      <c r="EA141" t="inlineStr">
+        <is>
+          <t>Νέες Αφίξεις</t>
+        </is>
+      </c>
+      <c r="EB141" t="inlineStr">
+        <is>
+          <t>Ανακάλυψε τα νέα κομμάτια</t>
+        </is>
+      </c>
+      <c r="EC141" t="inlineStr">
+        <is>
+          <t>Καλοκαίρι 2026</t>
+        </is>
+      </c>
+      <c r="EG141" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ141" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK141" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="DS142" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DT142" t="inlineStr">
+        <is>
+          <t>Advertiser</t>
+        </is>
+      </c>
+      <c r="DU142" t="inlineStr">
+        <is>
+          <t>Advertiser</t>
+        </is>
+      </c>
+      <c r="ED142" t="inlineStr">
         <is>
           <t>Brands</t>
         </is>
       </c>
-      <c r="EE106" t="inlineStr">
+      <c r="EE142" t="inlineStr">
         <is>
           <t>ARPYES
 CKONTOVA
@@ -6276,359 +7608,359 @@
 SALT AND PEPPER</t>
         </is>
       </c>
-      <c r="EG106" t="inlineStr">
-        <is>
-          <t>Enabled</t>
-        </is>
-      </c>
-      <c r="EJ106" t="inlineStr">
-        <is>
-          <t>Enabled</t>
-        </is>
-      </c>
-      <c r="EK106" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr">
+      <c r="EG142" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ142" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK142" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O107" t="inlineStr">
+      <c r="O143" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P107" t="inlineStr">
+      <c r="P143" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DS107" t="inlineStr">
+      <c r="DS143" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DT107" t="inlineStr">
+      <c r="DT143" t="inlineStr">
         <is>
           <t>Advertiser</t>
         </is>
       </c>
-      <c r="DU107" t="inlineStr">
+      <c r="DU143" t="inlineStr">
         <is>
           <t>Advertiser</t>
         </is>
       </c>
-      <c r="EF107" t="inlineStr">
+      <c r="EF143" t="inlineStr">
         <is>
           <t>Έως -30% Έκπτωση</t>
         </is>
       </c>
-      <c r="EG107" t="inlineStr">
-        <is>
-          <t>Enabled</t>
-        </is>
-      </c>
-      <c r="EJ107" t="inlineStr">
-        <is>
-          <t>Enabled</t>
-        </is>
-      </c>
-      <c r="EK107" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr">
+      <c r="EG143" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ143" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK143" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O108" t="inlineStr">
+      <c r="O144" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P108" t="inlineStr">
+      <c r="P144" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DS108" t="inlineStr">
+      <c r="DS144" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DT108" t="inlineStr">
+      <c r="DT144" t="inlineStr">
         <is>
           <t>Advertiser</t>
         </is>
       </c>
-      <c r="DU108" t="inlineStr">
+      <c r="DU144" t="inlineStr">
         <is>
           <t>Advertiser</t>
         </is>
       </c>
-      <c r="EF108" t="inlineStr">
+      <c r="EF144" t="inlineStr">
         <is>
           <t>Δωρεάν Επιστροφές</t>
         </is>
       </c>
-      <c r="EG108" t="inlineStr">
-        <is>
-          <t>Enabled</t>
-        </is>
-      </c>
-      <c r="EJ108" t="inlineStr">
-        <is>
-          <t>Enabled</t>
-        </is>
-      </c>
-      <c r="EK108" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr">
+      <c r="EG144" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ144" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK144" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O109" t="inlineStr">
+      <c r="O145" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P109" t="inlineStr">
+      <c r="P145" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DS109" t="inlineStr">
+      <c r="DS145" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DT109" t="inlineStr">
+      <c r="DT145" t="inlineStr">
         <is>
           <t>Advertiser</t>
         </is>
       </c>
-      <c r="DU109" t="inlineStr">
+      <c r="DU145" t="inlineStr">
         <is>
           <t>Advertiser</t>
         </is>
       </c>
-      <c r="EF109" t="inlineStr">
+      <c r="EF145" t="inlineStr">
         <is>
           <t>Παράδοση 2-3 Μέρες</t>
         </is>
       </c>
-      <c r="EG109" t="inlineStr">
-        <is>
-          <t>Enabled</t>
-        </is>
-      </c>
-      <c r="EJ109" t="inlineStr">
-        <is>
-          <t>Enabled</t>
-        </is>
-      </c>
-      <c r="EK109" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr">
+      <c r="EG145" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ145" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK145" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O110" t="inlineStr">
+      <c r="O146" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P110" t="inlineStr">
+      <c r="P146" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DS110" t="inlineStr">
+      <c r="DS146" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DT110" t="inlineStr">
+      <c r="DT146" t="inlineStr">
         <is>
           <t>Advertiser</t>
         </is>
       </c>
-      <c r="DU110" t="inlineStr">
+      <c r="DU146" t="inlineStr">
         <is>
           <t>Advertiser</t>
         </is>
       </c>
-      <c r="EF110" t="inlineStr">
+      <c r="EF146" t="inlineStr">
         <is>
           <t>Ασφαλείς Πληρωμές</t>
         </is>
       </c>
-      <c r="EG110" t="inlineStr">
-        <is>
-          <t>Enabled</t>
-        </is>
-      </c>
-      <c r="EJ110" t="inlineStr">
-        <is>
-          <t>Enabled</t>
-        </is>
-      </c>
-      <c r="EK110" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr">
+      <c r="EG146" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ146" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK146" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O111" t="inlineStr">
+      <c r="O147" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P111" t="inlineStr">
+      <c r="P147" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DS111" t="inlineStr">
+      <c r="DS147" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DT111" t="inlineStr">
+      <c r="DT147" t="inlineStr">
         <is>
           <t>Advertiser</t>
         </is>
       </c>
-      <c r="DU111" t="inlineStr">
+      <c r="DU147" t="inlineStr">
         <is>
           <t>Advertiser</t>
         </is>
       </c>
-      <c r="EF111" t="inlineStr">
+      <c r="EF147" t="inlineStr">
         <is>
           <t>5 Designer Brands σε Sale</t>
         </is>
       </c>
-      <c r="EG111" t="inlineStr">
-        <is>
-          <t>Enabled</t>
-        </is>
-      </c>
-      <c r="EJ111" t="inlineStr">
-        <is>
-          <t>Enabled</t>
-        </is>
-      </c>
-      <c r="EK111" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr">
+      <c r="EG147" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ147" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK147" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Valeri| Pmax| Eight - Summer Sales -2026</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="O112" t="inlineStr">
+      <c r="O148" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P112" t="inlineStr">
+      <c r="P148" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DS112" t="inlineStr">
+      <c r="DS148" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DT112" t="inlineStr">
+      <c r="DT148" t="inlineStr">
         <is>
           <t>Advertiser</t>
         </is>
       </c>
-      <c r="DU112" t="inlineStr">
+      <c r="DU148" t="inlineStr">
         <is>
           <t>Advertiser</t>
         </is>
       </c>
-      <c r="EF112" t="inlineStr">
+      <c r="EF148" t="inlineStr">
         <is>
           <t>Επώνυμα Ελληνικά Brands</t>
         </is>
       </c>
-      <c r="EG112" t="inlineStr">
-        <is>
-          <t>Enabled</t>
-        </is>
-      </c>
-      <c r="EJ112" t="inlineStr">
-        <is>
-          <t>Enabled</t>
-        </is>
-      </c>
-      <c r="EK112" t="inlineStr">
+      <c r="EG148" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EJ148" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="EK148" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
